--- a/GarantiTakip/tukNETinternet/Turknet-ödemeler.xlsx
+++ b/GarantiTakip/tukNETinternet/Turknet-ödemeler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\jcts\GarantiTakip\tukNETinternet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E449531-7DBF-4228-A042-58BD18A8995E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FC9EF5-185C-4DB6-9216-83A41FA6B2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="31">
   <si>
     <t>ödeme</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t>17 şubat 2025 - 17 şubat 2026 - 12 aylık Dönem</t>
-  </si>
-  <si>
-    <t>Toplam 13 lık ücret</t>
   </si>
   <si>
     <t>1 aylık geçmiş dönem borcu eklenerek</t>
@@ -141,6 +138,18 @@
   </si>
   <si>
     <t xml:space="preserve"> TL olmasına rağmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">989,78*6 = 5938,68 TL olarak yapılmıştır. </t>
+  </si>
+  <si>
+    <t>2025 yılı için 469,90 *12 = 5638,8 TL olması gerekirken</t>
+  </si>
+  <si>
+    <t>Toplam 13 aylık ücret</t>
+  </si>
+  <si>
+    <t>birim fiyat</t>
   </si>
 </sst>
 </file>
@@ -639,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="1" bestFit="1" customWidth="1"/>
@@ -648,18 +657,19 @@
     <col min="4" max="4" width="9" style="4" customWidth="1"/>
     <col min="5" max="7" width="9.140625" style="4"/>
     <col min="8" max="8" width="2.42578125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>5053202240</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
@@ -676,7 +686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45308</v>
       </c>
@@ -705,7 +715,7 @@
       <c r="L4" s="15"/>
       <c r="M4" s="16"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45320</v>
       </c>
@@ -723,7 +733,7 @@
         <v>3599.88</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" ref="G5:G31" si="0">G4+F5-E5</f>
+        <f t="shared" ref="G5:G32" si="0">G4+F5-E5</f>
         <v>3899.87</v>
       </c>
       <c r="I5" s="17" t="s">
@@ -734,7 +744,7 @@
       <c r="L5" s="18"/>
       <c r="M5" s="19"/>
     </row>
-    <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45320</v>
       </c>
@@ -756,7 +766,7 @@
       <c r="L6" s="6"/>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45327</v>
       </c>
@@ -771,7 +781,7 @@
         <v>3649.86</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45327</v>
       </c>
@@ -786,14 +796,14 @@
         <v>2999.88</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
       <c r="M8" s="16"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>7</v>
       </c>
@@ -807,7 +817,7 @@
       <c r="L9" s="18"/>
       <c r="M9" s="19"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>6</v>
       </c>
@@ -816,14 +826,14 @@
         <v>2999.88</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J10" s="18"/>
       <c r="K10" s="18"/>
       <c r="L10" s="18"/>
       <c r="M10" s="19"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45356</v>
       </c>
@@ -841,13 +851,15 @@
         <v>9</v>
       </c>
       <c r="J11" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="K11" s="18"/>
       <c r="L11" s="18"/>
       <c r="M11" s="19"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45356</v>
       </c>
@@ -874,7 +886,7 @@
       <c r="L12" s="18"/>
       <c r="M12" s="19"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45387</v>
       </c>
@@ -901,7 +913,7 @@
       <c r="L13" s="18"/>
       <c r="M13" s="19"/>
     </row>
-    <row r="14" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45387</v>
       </c>
@@ -917,7 +929,7 @@
       </c>
       <c r="I14" s="24"/>
       <c r="J14" s="25" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K14" s="26">
         <f>K13+K12</f>
@@ -925,8 +937,11 @@
       </c>
       <c r="L14" s="18"/>
       <c r="M14" s="19"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O14">
+        <v>22500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45417</v>
       </c>
@@ -945,8 +960,11 @@
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
       <c r="M15" s="19"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45417</v>
       </c>
@@ -967,6 +985,10 @@
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="19"/>
+      <c r="O16">
+        <f>O15*O14</f>
+        <v>270000</v>
+      </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1132,9 +1154,11 @@
         <v>9</v>
       </c>
       <c r="J24" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="K24" s="18"/>
       <c r="L24" s="18"/>
       <c r="M24" s="19"/>
     </row>
@@ -1163,7 +1187,7 @@
         <v>5638.7999999999993</v>
       </c>
       <c r="L25" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M25" s="19"/>
     </row>
@@ -1182,7 +1206,7 @@
         <v>1679.5779999999991</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J26" s="22"/>
       <c r="K26" s="22"/>
@@ -1236,7 +1260,10 @@
       <c r="L28" s="18"/>
       <c r="M28" s="19"/>
     </row>
-    <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>28</v>
+      </c>
       <c r="G29" s="4">
         <f t="shared" si="0"/>
         <v>-299.98800000000097</v>
@@ -1249,54 +1276,64 @@
       <c r="L29" s="18"/>
       <c r="M29" s="19"/>
     </row>
-    <row r="30" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="4">
-        <f t="shared" si="0"/>
-        <v>-299.98800000000097</v>
-      </c>
-      <c r="I30" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="J30" s="18" t="s">
-        <v>1</v>
-      </c>
+    <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="18"/>
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
       <c r="M30" s="19"/>
     </row>
-    <row r="31" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="13"/>
+    <row r="31" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="10"/>
       <c r="G31" s="4">
-        <f t="shared" si="0"/>
+        <f>G29+F31-E31</f>
         <v>-299.98800000000097</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="19"/>
+    </row>
+    <row r="32" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="4">
+        <f t="shared" si="0"/>
+        <v>-299.98800000000097</v>
+      </c>
+      <c r="I32" s="5">
         <v>6</v>
       </c>
-      <c r="J31" s="6">
+      <c r="J32" s="6">
         <v>989.78</v>
       </c>
-      <c r="K31" s="23">
-        <f>I31*J31</f>
+      <c r="K32" s="23">
+        <f>I32*J32</f>
         <v>5938.68</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="L32" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="M31" s="7"/>
+      <c r="M32" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GarantiTakip/tukNETinternet/Turknet-ödemeler.xlsx
+++ b/GarantiTakip/tukNETinternet/Turknet-ödemeler.xlsx
@@ -1,33 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\jcts\GarantiTakip\tukNETinternet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\comprg\bvaagitme\jcts\GarantiTakip\tukNETinternet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FC9EF5-185C-4DB6-9216-83A41FA6B2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7CA195-BC69-452F-B645-003269556FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -223,13 +214,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -326,15 +317,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -357,17 +345,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -670,19 +669,19 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="24" t="s">
         <v>2</v>
       </c>
     </row>
@@ -707,13 +706,13 @@
         <f>F4-E4</f>
         <v>299.99</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="16"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="13"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -736,13 +735,13 @@
         <f t="shared" ref="G5:G32" si="0">G4+F5-E5</f>
         <v>3899.87</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="I5" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="19"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="31"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
@@ -751,20 +750,20 @@
       <c r="B6" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="22">
         <v>299.99</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" si="0"/>
         <v>3599.88</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="7"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="34"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
@@ -788,20 +787,20 @@
       <c r="B8" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="22">
         <v>649.98</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
         <v>2999.88</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="16"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="13"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
@@ -811,11 +810,8 @@
         <f t="shared" si="0"/>
         <v>2999.88</v>
       </c>
-      <c r="I9" s="17"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="19"/>
+      <c r="I9" s="14"/>
+      <c r="M9" s="15"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
@@ -825,13 +821,10 @@
         <f t="shared" si="0"/>
         <v>2999.88</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="I10" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="19"/>
+      <c r="M10" s="15"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -847,17 +840,16 @@
         <f t="shared" si="0"/>
         <v>3049.86</v>
       </c>
-      <c r="I11" s="17" t="s">
+      <c r="I11" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="J11" t="s">
         <v>30</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="18"/>
-      <c r="M11" s="19"/>
+      <c r="M11" s="15"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -866,25 +858,24 @@
       <c r="B12" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="22">
         <v>649.98</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="0"/>
         <v>2399.88</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="14">
         <v>12</v>
       </c>
-      <c r="J12" s="18">
+      <c r="J12">
         <v>299.99</v>
       </c>
-      <c r="K12" s="18">
+      <c r="K12">
         <f>I12*J12</f>
         <v>3599.88</v>
       </c>
-      <c r="L12" s="18"/>
-      <c r="M12" s="19"/>
+      <c r="M12" s="15"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -900,18 +891,17 @@
         <f t="shared" si="0"/>
         <v>2449.86</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="14">
         <v>1</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13">
         <v>299.99</v>
       </c>
-      <c r="K13" s="18">
+      <c r="K13">
         <f>I13*J13</f>
         <v>299.99</v>
       </c>
-      <c r="L13" s="18"/>
-      <c r="M13" s="19"/>
+      <c r="M13" s="15"/>
     </row>
     <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -920,23 +910,22 @@
       <c r="B14" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="22">
         <v>649.98</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="0"/>
         <v>1799.88</v>
       </c>
-      <c r="I14" s="24"/>
-      <c r="J14" s="25" t="s">
+      <c r="I14" s="19"/>
+      <c r="J14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="K14" s="26">
+      <c r="K14" s="21">
         <f>K13+K12</f>
         <v>3899.87</v>
       </c>
-      <c r="L14" s="18"/>
-      <c r="M14" s="19"/>
+      <c r="M14" s="15"/>
       <c r="O14">
         <v>22500</v>
       </c>
@@ -955,11 +944,8 @@
         <f t="shared" si="0"/>
         <v>1849.8700000000001</v>
       </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="19"/>
+      <c r="I15" s="14"/>
+      <c r="M15" s="15"/>
       <c r="O15">
         <v>12</v>
       </c>
@@ -971,20 +957,17 @@
       <c r="B16" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="22">
         <v>649.98</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="0"/>
         <v>1199.8900000000001</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="19"/>
+      <c r="M16" s="15"/>
       <c r="O16">
         <f>O15*O14</f>
         <v>270000</v>
@@ -1004,15 +987,13 @@
         <f t="shared" si="0"/>
         <v>1249.8800000000001</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I17" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J17" s="18" t="s">
+      <c r="J17" t="s">
         <v>1</v>
       </c>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="19"/>
+      <c r="M17" s="15"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
@@ -1021,27 +1002,27 @@
       <c r="B18" t="s">
         <v>3</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="22">
         <v>649.98</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="0"/>
         <v>599.90000000000009</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="25">
         <v>6</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="26">
         <v>649.98</v>
       </c>
-      <c r="K18" s="23">
+      <c r="K18" s="27">
         <f>I18*J18</f>
         <v>3899.88</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="M18" s="7"/>
+      <c r="M18" s="28"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -1065,7 +1046,7 @@
       <c r="B20" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="22">
         <v>649.98</v>
       </c>
       <c r="G20" s="4">
@@ -1094,13 +1075,13 @@
         <f t="shared" si="0"/>
         <v>5638.7099999999991</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="I21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="16"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="13"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
@@ -1108,11 +1089,8 @@
         <f t="shared" si="0"/>
         <v>5638.7099999999991</v>
       </c>
-      <c r="I22" s="17"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="19"/>
+      <c r="I22" s="14"/>
+      <c r="M22" s="15"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -1128,13 +1106,10 @@
         <f t="shared" si="0"/>
         <v>4648.9269999999988</v>
       </c>
-      <c r="I23" s="17" t="s">
+      <c r="I23" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="19"/>
+      <c r="M23" s="15"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1150,17 +1125,16 @@
         <f t="shared" si="0"/>
         <v>3659.1439999999989</v>
       </c>
-      <c r="I24" s="17" t="s">
+      <c r="I24" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="J24" s="18" t="s">
+      <c r="J24" t="s">
         <v>30</v>
       </c>
-      <c r="K24" s="18" t="s">
+      <c r="K24" t="s">
         <v>1</v>
       </c>
-      <c r="L24" s="18"/>
-      <c r="M24" s="19"/>
+      <c r="M24" s="15"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -1176,20 +1150,20 @@
         <f t="shared" si="0"/>
         <v>2669.360999999999</v>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="14">
         <v>12</v>
       </c>
-      <c r="J25" s="18">
+      <c r="J25">
         <v>469.9</v>
       </c>
-      <c r="K25" s="20">
+      <c r="K25" s="16">
         <f>I25*J25</f>
         <v>5638.7999999999993</v>
       </c>
-      <c r="L25" s="18" t="s">
+      <c r="L25" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="19"/>
+      <c r="M25" s="15"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -1205,13 +1179,13 @@
         <f t="shared" si="0"/>
         <v>1679.5779999999991</v>
       </c>
-      <c r="I26" s="21" t="s">
+      <c r="I26" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="19"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="15"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
@@ -1227,18 +1201,18 @@
         <f t="shared" si="0"/>
         <v>689.79499999999905</v>
       </c>
-      <c r="I27" s="21">
+      <c r="I27" s="17">
         <v>1</v>
       </c>
-      <c r="J27" s="22">
+      <c r="J27" s="18">
         <v>299.89999999999998</v>
       </c>
-      <c r="K27" s="22">
+      <c r="K27" s="18">
         <f>I27*J27</f>
         <v>299.89999999999998</v>
       </c>
-      <c r="L27" s="22"/>
-      <c r="M27" s="19"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="15"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
@@ -1254,11 +1228,8 @@
         <f t="shared" si="0"/>
         <v>-299.98800000000097</v>
       </c>
-      <c r="I28" s="17"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
-      <c r="M28" s="19"/>
+      <c r="I28" s="14"/>
+      <c r="M28" s="15"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
@@ -1268,72 +1239,64 @@
         <f t="shared" si="0"/>
         <v>-299.98800000000097</v>
       </c>
-      <c r="I29" s="17" t="s">
+      <c r="I29" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="19"/>
+      <c r="M29" s="15"/>
     </row>
     <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>27</v>
       </c>
-      <c r="I30" s="17"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="19"/>
+      <c r="I30" s="14"/>
+      <c r="M30" s="15"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="10"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="7"/>
       <c r="G31" s="4">
         <f>G29+F31-E31</f>
         <v>-299.98800000000097</v>
       </c>
-      <c r="I31" s="17" t="s">
+      <c r="I31" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J31" s="18" t="s">
+      <c r="J31" t="s">
         <v>1</v>
       </c>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="19"/>
+      <c r="M31" s="15"/>
     </row>
     <row r="32" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="13"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="10"/>
       <c r="G32" s="4">
         <f t="shared" si="0"/>
         <v>-299.98800000000097</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I32" s="25">
         <v>6</v>
       </c>
-      <c r="J32" s="6">
+      <c r="J32" s="26">
         <v>989.78</v>
       </c>
-      <c r="K32" s="23">
+      <c r="K32" s="27">
         <f>I32*J32</f>
         <v>5938.68</v>
       </c>
-      <c r="L32" s="6" t="s">
+      <c r="L32" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="M32" s="7"/>
+      <c r="M32" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
